--- a/apps/api/data/excel_templates/degrees.xlsx
+++ b/apps/api/data/excel_templates/degrees.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BEA371-E062-E743-A1E7-E1844E046EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73480B4-3EA2-F64C-A18F-5F3CBA77F68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="20740" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="degrees" sheetId="1" r:id="rId1"/>
@@ -1576,12 +1576,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1887,7 +1889,9 @@
   <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="18" customWidth="1"/>
+    <col min="1" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" style="4" customWidth="1"/>
+    <col min="6" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1903,7 +1907,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1929,7 +1933,7 @@
       <c r="D2" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1949,7 +1953,7 @@
       <c r="D3" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1969,7 +1973,7 @@
       <c r="D4" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -1989,7 +1993,7 @@
       <c r="D5" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -2009,7 +2013,7 @@
       <c r="D6" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -2029,7 +2033,7 @@
       <c r="D7" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>2</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -2049,7 +2053,7 @@
       <c r="D8" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>2</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -2069,7 +2073,7 @@
       <c r="D9" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>2</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -2089,7 +2093,7 @@
       <c r="D10" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="4">
         <v>2</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -2109,7 +2113,7 @@
       <c r="D11" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="4">
         <v>2</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -2129,7 +2133,7 @@
       <c r="D12" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="4">
         <v>2</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -2149,7 +2153,7 @@
       <c r="D13" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="4">
         <v>2</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -2169,7 +2173,7 @@
       <c r="D14" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="4">
         <v>2</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -2189,7 +2193,7 @@
       <c r="D15" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="4">
         <v>2</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -2209,7 +2213,7 @@
       <c r="D16" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="4">
         <v>2</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -2229,7 +2233,7 @@
       <c r="D17" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="4">
         <v>2</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -2249,7 +2253,7 @@
       <c r="D18" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="4">
         <v>2</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -2269,7 +2273,7 @@
       <c r="D19" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="4">
         <v>2</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -2289,7 +2293,7 @@
       <c r="D20" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="4">
         <v>2</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -2309,7 +2313,7 @@
       <c r="D21" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="4">
         <v>2</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -2329,7 +2333,7 @@
       <c r="D22" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="4">
         <v>2</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -2349,7 +2353,7 @@
       <c r="D23" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="4">
         <v>2</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -2369,7 +2373,7 @@
       <c r="D24" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="4">
         <v>2</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -2389,7 +2393,7 @@
       <c r="D25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="4">
         <v>2</v>
       </c>
       <c r="F25" s="2" t="s">
@@ -2409,7 +2413,7 @@
       <c r="D26" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="4">
         <v>2</v>
       </c>
       <c r="F26" s="2" t="s">
@@ -2429,7 +2433,7 @@
       <c r="D27" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="4">
         <v>2</v>
       </c>
       <c r="F27" s="2" t="s">
@@ -2449,7 +2453,7 @@
       <c r="D28" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="4">
         <v>2</v>
       </c>
       <c r="F28" s="2" t="s">
@@ -2469,7 +2473,7 @@
       <c r="D29" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="4">
         <v>2</v>
       </c>
       <c r="F29" s="2" t="s">
@@ -2489,7 +2493,7 @@
       <c r="D30" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="4">
         <v>2</v>
       </c>
       <c r="F30" s="2" t="s">
@@ -2509,7 +2513,7 @@
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="4">
         <v>4</v>
       </c>
       <c r="F31" s="2" t="s">
@@ -2529,7 +2533,7 @@
       <c r="D32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="4">
         <v>4</v>
       </c>
       <c r="F32" s="2" t="s">
@@ -2549,7 +2553,7 @@
       <c r="D33" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="4">
         <v>4</v>
       </c>
       <c r="F33" s="2" t="s">
@@ -2569,7 +2573,7 @@
       <c r="D34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="4">
         <v>4</v>
       </c>
       <c r="F34" s="2" t="s">
@@ -2589,7 +2593,7 @@
       <c r="D35" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="4">
         <v>4</v>
       </c>
       <c r="F35" s="2" t="s">
@@ -2609,7 +2613,7 @@
       <c r="D36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="4">
         <v>4</v>
       </c>
       <c r="F36" s="2" t="s">
@@ -2629,7 +2633,7 @@
       <c r="D37" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="4">
         <v>4</v>
       </c>
       <c r="F37" s="2" t="s">
@@ -2649,7 +2653,7 @@
       <c r="D38" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="4">
         <v>4</v>
       </c>
       <c r="F38" s="2" t="s">
@@ -2669,7 +2673,7 @@
       <c r="D39" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="4">
         <v>4</v>
       </c>
       <c r="F39" s="2" t="s">
@@ -2689,7 +2693,7 @@
       <c r="D40" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="4">
         <v>4</v>
       </c>
       <c r="F40" s="2" t="s">
@@ -2709,7 +2713,7 @@
       <c r="D41" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="4">
         <v>4</v>
       </c>
       <c r="F41" s="2" t="s">
@@ -2729,7 +2733,7 @@
       <c r="D42" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="4">
         <v>4</v>
       </c>
       <c r="F42" s="2" t="s">
@@ -2749,7 +2753,7 @@
       <c r="D43" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="4">
         <v>4</v>
       </c>
       <c r="F43" s="2" t="s">
@@ -2769,7 +2773,7 @@
       <c r="D44" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="4">
         <v>4</v>
       </c>
       <c r="F44" s="2" t="s">
@@ -2789,7 +2793,7 @@
       <c r="D45" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="4">
         <v>4</v>
       </c>
       <c r="F45" s="2" t="s">
@@ -2809,7 +2813,7 @@
       <c r="D46" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="4">
         <v>4</v>
       </c>
       <c r="F46" s="2" t="s">
@@ -2829,7 +2833,7 @@
       <c r="D47" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="4">
         <v>4</v>
       </c>
       <c r="F47" s="2" t="s">
@@ -2849,7 +2853,7 @@
       <c r="D48" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="4">
         <v>4</v>
       </c>
       <c r="F48" s="2" t="s">
@@ -2869,7 +2873,7 @@
       <c r="D49" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="4">
         <v>4</v>
       </c>
       <c r="F49" s="2" t="s">
@@ -2889,7 +2893,7 @@
       <c r="D50" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="4">
         <v>4</v>
       </c>
       <c r="F50" s="2" t="s">
@@ -2909,7 +2913,7 @@
       <c r="D51" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="4">
         <v>4</v>
       </c>
       <c r="F51" s="2" t="s">
@@ -2929,7 +2933,7 @@
       <c r="D52" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="4">
         <v>4</v>
       </c>
       <c r="F52" s="2" t="s">
@@ -2949,7 +2953,7 @@
       <c r="D53" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="4">
         <v>4</v>
       </c>
       <c r="F53" s="2" t="s">
@@ -2969,7 +2973,7 @@
       <c r="D54" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="4">
         <v>4</v>
       </c>
       <c r="F54" s="2" t="s">
@@ -2989,7 +2993,7 @@
       <c r="D55" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="4">
         <v>4</v>
       </c>
       <c r="F55" s="2" t="s">
@@ -3009,7 +3013,7 @@
       <c r="D56" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="4">
         <v>4</v>
       </c>
       <c r="F56" s="2" t="s">
@@ -3029,7 +3033,7 @@
       <c r="D57" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="4">
         <v>4</v>
       </c>
       <c r="F57" s="2" t="s">
@@ -3049,7 +3053,7 @@
       <c r="D58" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="4">
         <v>4</v>
       </c>
       <c r="F58" s="2" t="s">
@@ -3069,7 +3073,7 @@
       <c r="D59" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="4">
         <v>4</v>
       </c>
       <c r="F59" s="2" t="s">
@@ -3089,7 +3093,7 @@
       <c r="D60" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="4">
         <v>4</v>
       </c>
       <c r="F60" s="2" t="s">
@@ -3109,7 +3113,7 @@
       <c r="D61" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="4">
         <v>4</v>
       </c>
       <c r="F61" s="2" t="s">
@@ -3129,7 +3133,7 @@
       <c r="D62" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="4">
         <v>3</v>
       </c>
       <c r="F62" s="2" t="s">
@@ -3149,7 +3153,7 @@
       <c r="D63" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="4">
         <v>3</v>
       </c>
       <c r="F63" s="2" t="s">
@@ -3169,7 +3173,7 @@
       <c r="D64" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="4">
         <v>3</v>
       </c>
       <c r="F64" s="2" t="s">
@@ -3189,7 +3193,7 @@
       <c r="D65" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="4">
         <v>3</v>
       </c>
       <c r="F65" s="2" t="s">
@@ -3209,7 +3213,7 @@
       <c r="D66" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="4">
         <v>3</v>
       </c>
       <c r="F66" s="2" t="s">
@@ -3229,7 +3233,7 @@
       <c r="D67" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="4">
         <v>3</v>
       </c>
       <c r="F67" s="2" t="s">
@@ -3249,7 +3253,7 @@
       <c r="D68" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="4">
         <v>3</v>
       </c>
       <c r="F68" s="2" t="s">
@@ -3269,7 +3273,7 @@
       <c r="D69" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="4">
         <v>3</v>
       </c>
       <c r="F69" s="2" t="s">
@@ -3289,7 +3293,7 @@
       <c r="D70" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="4">
         <v>3</v>
       </c>
       <c r="F70" s="2" t="s">
@@ -3309,7 +3313,7 @@
       <c r="D71" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="4">
         <v>3</v>
       </c>
       <c r="F71" s="2" t="s">
@@ -3329,7 +3333,7 @@
       <c r="D72" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="4">
         <v>3</v>
       </c>
       <c r="F72" s="2" t="s">
@@ -3349,7 +3353,7 @@
       <c r="D73" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="4">
         <v>3</v>
       </c>
       <c r="F73" s="2" t="s">
@@ -3369,7 +3373,7 @@
       <c r="D74" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="4">
         <v>3</v>
       </c>
       <c r="F74" s="2" t="s">
@@ -3389,7 +3393,7 @@
       <c r="D75" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="4">
         <v>3</v>
       </c>
       <c r="F75" s="2" t="s">
@@ -3409,7 +3413,7 @@
       <c r="D76" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="4">
         <v>3</v>
       </c>
       <c r="F76" s="2" t="s">
@@ -3429,7 +3433,7 @@
       <c r="D77" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="4">
         <v>3</v>
       </c>
       <c r="F77" s="2" t="s">
@@ -3449,7 +3453,7 @@
       <c r="D78" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="4">
         <v>3</v>
       </c>
       <c r="F78" s="2" t="s">
@@ -3469,7 +3473,7 @@
       <c r="D79" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="4">
         <v>3</v>
       </c>
       <c r="F79" s="2" t="s">
@@ -3489,7 +3493,7 @@
       <c r="D80" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="4">
         <v>3</v>
       </c>
       <c r="F80" s="2" t="s">
@@ -3509,7 +3513,7 @@
       <c r="D81" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="4">
         <v>2</v>
       </c>
       <c r="F81" s="2" t="s">
@@ -3529,7 +3533,7 @@
       <c r="D82" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="4">
         <v>2</v>
       </c>
       <c r="F82" s="2" t="s">
@@ -3549,7 +3553,7 @@
       <c r="D83" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="4">
         <v>2</v>
       </c>
       <c r="F83" s="2" t="s">
@@ -3569,7 +3573,7 @@
       <c r="D84" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="4">
         <v>2</v>
       </c>
       <c r="F84" s="2" t="s">
@@ -3589,7 +3593,7 @@
       <c r="D85" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="4">
         <v>2</v>
       </c>
       <c r="F85" s="2" t="s">
@@ -3609,7 +3613,7 @@
       <c r="D86" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="4">
         <v>2</v>
       </c>
       <c r="F86" s="2" t="s">
@@ -3629,7 +3633,7 @@
       <c r="D87" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="4">
         <v>2</v>
       </c>
       <c r="F87" s="2" t="s">
@@ -3649,7 +3653,7 @@
       <c r="D88" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="4">
         <v>2</v>
       </c>
       <c r="F88" s="2" t="s">
@@ -3669,7 +3673,7 @@
       <c r="D89" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="4">
         <v>2</v>
       </c>
       <c r="F89" s="2" t="s">
@@ -3689,7 +3693,7 @@
       <c r="D90" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="4">
         <v>2</v>
       </c>
       <c r="F90" s="2" t="s">
@@ -3709,7 +3713,7 @@
       <c r="D91" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="4">
         <v>2</v>
       </c>
       <c r="F91" s="2" t="s">
@@ -3729,7 +3733,7 @@
       <c r="D92" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="4">
         <v>2</v>
       </c>
       <c r="F92" s="2" t="s">
@@ -3749,7 +3753,7 @@
       <c r="D93" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="4">
         <v>2</v>
       </c>
       <c r="F93" s="2" t="s">
@@ -3769,7 +3773,7 @@
       <c r="D94" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="4">
         <v>2</v>
       </c>
       <c r="F94" s="2" t="s">
@@ -3789,7 +3793,7 @@
       <c r="D95" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="4">
         <v>2</v>
       </c>
       <c r="F95" s="2" t="s">
@@ -3809,7 +3813,7 @@
       <c r="D96" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="4">
         <v>2</v>
       </c>
       <c r="F96" s="2" t="s">
@@ -3829,7 +3833,7 @@
       <c r="D97" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="4">
         <v>2</v>
       </c>
       <c r="F97" s="2" t="s">
@@ -3849,7 +3853,7 @@
       <c r="D98" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="4">
         <v>2</v>
       </c>
       <c r="F98" s="2" t="s">
@@ -3869,7 +3873,7 @@
       <c r="D99" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="4">
         <v>2</v>
       </c>
       <c r="F99" s="2" t="s">
@@ -3889,7 +3893,7 @@
       <c r="D100" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="4">
         <v>2</v>
       </c>
       <c r="F100" s="2" t="s">
@@ -3909,7 +3913,7 @@
       <c r="D101" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="4">
         <v>2</v>
       </c>
       <c r="F101" s="2" t="s">

--- a/apps/api/data/excel_templates/degrees.xlsx
+++ b/apps/api/data/excel_templates/degrees.xlsx
@@ -3722,7 +3722,7 @@
       <c r="H101" s="5" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:H1"/>
   <conditionalFormatting sqref="E2:E101">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">

--- a/apps/api/data/excel_templates/degrees.xlsx
+++ b/apps/api/data/excel_templates/degrees.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection lockStructure="1"/>
+  <workbookProtection workbookPassword="DB2D" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -491,7 +491,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
   <autoFilter ref="A1:H1"/>
   <dataValidations count="3">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">

--- a/apps/api/data/excel_templates/degrees.xlsx
+++ b/apps/api/data/excel_templates/degrees.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -70,6 +70,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -489,6 +492,3206 @@
           <t>metadata</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Master in Philosophy and English Literature</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000001</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Literature &amp; Philosophy</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on literary and philosophical texts. Develops analytical and interpretive skills. Studies cultural theory. Emphasises critical reading. Prepares for academic careers.</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Master in Philosophy and Mathematics</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000002</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Mathematical Philosophy</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on logic and mathematical reasoning. Develops analytical and abstract thinking. Studies formal systems. Emphasises theoretical inquiry. Prepares for research careers.</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Master in Philosophy and Public Policy</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000003</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Policy Studies</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on ethical foundations of policy-making. Develops analytical and governance skills. Studies public systems. Emphasises decision frameworks. Prepares for policy roles.</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Master in Philosophy and Religion</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000004</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Religious Studies</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on philosophical analysis of religion. Develops interpretive and critical skills. Studies belief systems. Emphasises theological inquiry. Prepares for academic roles.</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Master in Photonics</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000005</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Physics &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on light manipulation and optical systems. Develops experimental and theoretical skills. Studies wave optics. Emphasises applied physics. Prepares for research roles.</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Master in Photonics and Quantum Sciences</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000006</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Quantum Technology</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on quantum optics and photonics. Develops theoretical and experimental skills. Studies quantum systems. Emphasises advanced research. Prepares for scientific careers.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Master in Physical Sciences</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000007</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on physics and related sciences. Develops analytical and experimental skills. Studies matter and energy. Emphasises research methods. Prepares for scientific careers.</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Master in Physical Therapy and Rehabilitation</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000008</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Rehabilitation Science</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on restoring physical function after injury. Develops therapeutic skills. Studies movement recovery. Emphasises clinical rehabilitation. Prepares for therapy careers.</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Master in Physics and Technology of Nanostructures</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000009</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Nanotechnology</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on engineered nanoscale structures. Develops experimental and fabrication skills. Studies quantum effects. Emphasises advanced materials. Prepares for research roles.</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Master in Physics and Thermal Physics of Innovative Nuclear Power Installations</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000010</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Nuclear Energy</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on thermal and reactor physics. Develops modelling and engineering skills. Studies nuclear systems. Emphasises energy innovation. Prepares for nuclear industry roles.</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Master in Physics of Complex Systems and Biophysics</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000011</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Biophysics</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on complex systems in biology and physics. Develops analytical skills. Studies living systems. Emphasises interdisciplinary research. Prepares for scientific careers.</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Master in Physics with Mathematics</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000012</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Mathematical Physics</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on mathematical methods in physics. Develops modelling and analytical skills. Studies theoretical frameworks. Emphasises problem-solving. Prepares for research roles.</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Master in Physics with Planetary and Space Physics</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000013</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Space Physics</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on planetary systems and space environments. Develops analytical skills. Studies solar and planetary physics. Emphasises space science. Prepares for research careers.</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Master in Planning and Management of Tourism Systems</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000014</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Tourism Management</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on tourism system design and management. Develops planning and business skills. Studies tourism flows. Emphasises sustainability. Prepares for tourism industry roles.</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Master in Plasma Physics, Spectroscopy and Self-Organization</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000015</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Applied Physics</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on plasma diagnostics and systems behaviour. Develops analytical skills. Studies light-matter interaction. Emphasises advanced research. Prepares for physics careers.</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Master in Play Therapy</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000016</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Psychotherapy</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on therapeutic use of play for children. Develops counselling skills. Studies child psychology. Emphasises emotional development. Prepares for clinical therapy roles.</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Master in Podiatric Surgery</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000017</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Surgical Medicine</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on surgical treatment of foot disorders. Develops clinical and surgical skills. Studies anatomy and pathology. Emphasises operative care. Prepares for surgical roles.</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Master in Portuguese and Business</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000018</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Business Communication</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on Portuguese language in business contexts. Develops communication skills. Studies commerce and culture. Emphasises international trade. Prepares for business roles.</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Master in Post-production with Sound Design</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000019</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Media Production</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on audio post-production for media. Develops technical and creative skills. Studies sound design. Emphasises film and media industries. Prepares for production roles.</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Master in Power, Electronic and Telecommunication Engineering</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000020</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on integrated power and communication systems. Develops technical skills. Studies networks and electronics. Emphasises infrastructure. Prepares for engineering roles.</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Master in Process Engineering</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000021</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Chemical/Industrial Engineering</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on industrial process design and optimisation. Develops engineering skills. Studies production systems. Emphasises efficiency and safety. Prepares for industry roles.</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Master in Professional Archaeology and Comprehensive Heritage Management</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000022</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Archaeology</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on archaeological practice and heritage management. Develops field skills. Studies cultural preservation. Emphasises applied archaeology. Prepares for heritage roles.</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Master in Professional Non-surgical Aesthetic Practice</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000023</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Aesthetic Medicine</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on cosmetic non-surgical treatments. Develops clinical and procedural skills. Studies skin aesthetics. Emphasises patient care. Prepares for aesthetic practice roles.</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Master in Professional Studies in Education</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000024</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on advanced teaching and learning practice. Develops pedagogical skills. Studies education systems. Emphasises instructional improvement. Prepares for educator roles.</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Master in Professional Translation Studies</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000025</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Translation Studies</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on advanced translation theory and practice. Develops language skills. Studies translation techniques. Emphasises accuracy and fluency. Prepares for translator roles.</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Master in Prostate Cancer Care</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000026</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Oncology</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on diagnosis and treatment of prostate cancer. Develops clinical skills. Studies oncology care pathways. Emphasises patient management. Prepares for healthcare roles.</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Master in Psychology Conversion</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000027</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Conversion Psychology</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on foundational psychology training. Develops core analytical skills. Studies psychological theory. Emphasises transition into field. Prepares for psychology careers.</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Master in Psycho-oncology and Palliative Care</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000028</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Health Psychology</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on psychological support in cancer care. Develops clinical intervention skills. Studies patient wellbeing. Emphasises end-of-life care. Prepares for healthcare roles.</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Master in Public Health, Public Health Nutrition and Epidemiology</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000029</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Public Health Nutrition</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on nutrition and disease prevention. Develops epidemiological skills. Studies diet and population health. Emphasises prevention strategies. Prepares for health roles.</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Design in Visual Communication and BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000030</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Design / Communication</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Combines visual communication with global studies. Covers branding and media. Develops creative skills. Prepares for design careers.</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Teaching and BA in Mathematics</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000031</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Education / Mathematics</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Combines teaching with mathematics. Covers pedagogy and quantitative skills. Develops instructional ability. Prepares for teaching roles.</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Health Science in Traditional Chinese Medicine and BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000032</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Health / Traditional Medicine</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Combines Chinese medicine with global studies. Covers holistic health systems. Develops clinical knowledge. Prepares for healthcare roles.</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Teaching and BA in Visual Arts</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000033</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Education / Arts</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Combines teaching with visual arts practice. Covers pedagogy and creativity. Develops instructional skills. Prepares for arts education roles.</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Education and BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000034</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Combines teaching qualifications with global studies. Covers pedagogy and culture. Develops instructional skills. Prepares for education roles.</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Teaching and BA in Technology</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000035</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Education / Technology</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Combines teaching with technology studies. Covers digital tools and pedagogy. Develops instructional skills. Prepares for STEM education roles.</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Journalism and Professional Writing and BA in Creative Writing and Literature</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000036</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Journalism / Writing</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Combines journalism with creative writing. Covers reporting, storytelling, and media. Develops communication skills. Prepares for media careers.</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Commerce, BA in Psychology</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000037</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Business / Psychology</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Combines commerce with psychology studies. Covers business strategy and human behaviour. Develops analytical skills. Prepares for corporate roles.</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Nursing and BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000038</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Combines nursing practice with global studies. Covers healthcare systems and patient care. Develops clinical skills. Prepares for nursing careers.</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Teaching and BA in Humanities</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000039</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Combines teaching qualification with humanities studies. Covers pedagogy and culture. Develops instructional skills. Prepares for education roles.</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Design in Interior Architecture and BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000040</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Design / Architecture</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Combines interior design with global studies. Covers spatial design and culture. Develops creative and technical skills. Prepares for design careers.</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Design in Product Design and BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000041</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Design / Product</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Combines product design with global studies. Covers innovation and user-centred design. Develops technical skills. Prepares for design industry roles.</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Medical Science and BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000042</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Medical Science</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Combines medical science with global studies. Covers biology, health systems, and policy. Develops scientific skills. Prepares for health sector roles.</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Design in Animation and BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000043</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Design / International Studies</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Combines animation with global cultural studies. Covers storytelling and media production. Develops creative skills. Prepares for animation and media roles.</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Design in Photography and BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000044</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Design / Photography</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Combines photography with international studies. Covers visual storytelling and culture. Develops artistic skills. Prepares for media and photography roles.</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Commerce and BA in Psychology and Economics</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000045</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Business / Social Science</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Integrates commerce, psychology, and economics. Covers markets, behaviour, and policy. Develops analytical skills. Prepares for finance and consulting roles.</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Communication in Creative Writing and BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000046</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Communication / International Studies</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Combines creative writing with global studies. Covers media, culture, and communication. Develops storytelling skills. Prepares for media and international roles.</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Construction Project Management, BA in International Studies</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000047</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Construction / International Studies</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Combines construction management with global studies. Covers planning, infrastructure, and policy. Develops leadership skills. Prepares for project management roles.</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Commerce and BA in Psychology</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000048</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Business / Psychology</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Combines business commerce with psychological science. Covers markets, behaviour, and analytics. Develops interdisciplinary skills. Prepares for business and HR roles.</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor in Transfer Degree</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000049</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>General Studies</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Provides foundational academic coursework for transfer. Develops core academic skills. Focuses on university progression pathways. Prepares students for advanced degrees.</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor and MBA in Supply Chain Management</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000050</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Business / Logistics</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Integrated program covering supply chain and advanced business management. Covers logistics, operations, and strategy. Develops leadership skills. Prepares for senior management roles.</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Law with English Language Studies</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000051</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>English Studies</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Combines law with advanced study of English linguistics and usage. Builds strong written and verbal reasoning. Prepares for careers in law, media, publishing, or public administration.</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Law with English</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000052</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Combines law with English language and literature studies. Strengthens critical thinking, analysis, and communication. Prepares for careers in law, publishing, education, or media industries.</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Law with Classical Studies</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000053</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Classical Studies</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>Integrates law with ancient Greek and Roman civilizations. Develops analytical and historical interpretation skills. Prepares for careers in law, academia, heritage, or cultural policy sectors.</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Law with Criminology</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000054</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Criminology</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Combines law with the study of crime, justice, and society. Develops understanding of criminal behavior and legal responses. Leads to careers in policing, legal practice, or criminal justice policy.</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Forestry Transfer</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000055</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Forestry (Transfer Program)</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Provides foundational forestry education for academic transfer pathways. Develops basic ecological and scientific skills. Prepares students for advanced forestry studies. Strengthens academic readiness. Supports progression into specialized forestry degrees.</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Language and Literature Education</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000056</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Education &amp; Language</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on teaching languages and literature. Builds pedagogy and communication skills. Graduates work as language teachers.</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Mathematics with Education</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000057</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Mathematics Education</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on mathematics teaching and learning methods. Builds pedagogical skills. Graduates work in schools or education roles.</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Italian and Persian</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000058</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Language Studies</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Combines Italian and Persian languages. Builds intercultural communication skills. Graduates work in translation and diplomacy.</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of Medical Studies and Doctor of Medicine</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000059</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Medical Pathway</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>Integrated medical training program. Builds clinical and scientific expertise. Graduates become licensed medical practitioners.</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor of History Teaching</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000060</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Studies methods of teaching history. Develops pedagogical skills. Focuses on classroom instruction. Graduates work as educators.</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Fluids Engineering</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000061</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Studies fluid flow and engineering system design. Develops expertise in computational modeling and experimental research. Focuses on industrial and energy applications. Graduates work in research, aerospace, and engineering firms.</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Food and Biochemical Technology</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000062</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Food Science</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Combines food science with biochemical technologies. Develops expertise in food processing and biochemical research. Focuses on improving food quality and innovation. Graduates work in academia, biotechnology, and food industries.</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="n"/>
+      <c r="H63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Food Systems</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000063</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Food Systems</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Explores food production, distribution, and consumption systems. Develops interdisciplinary research and policy skills. Focuses on sustainability and resilience. Graduates work in academia, government, and nonprofit organizations.</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="n"/>
+      <c r="H64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Gender Studies</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000064</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Gender Studies</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Explores gender through social, political, and cultural research. Develops critical thinking and interdisciplinary research skills. Focuses on identity and equality. Graduates work in academia, policy, and community organizations.</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="6" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Geodesy and Geoinformatics</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000065</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Geospatial Science</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Combines geodesy with digital geographic information systems. Develops expertise in spatial analysis and geospatial technologies. Focuses on Earth measurement and mapping. Graduates work in academia, surveying, and GIS industries.</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="n"/>
+      <c r="H66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Geography and Earth Science</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000066</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Earth Science</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Combines geography with Earth science research. Develops expertise in environmental systems and geospatial analysis. Focuses on understanding Earth's processes. Graduates work in academia, environmental consulting, and government.</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="n"/>
+      <c r="H67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Geometry and Topology</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000067</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Studies the properties and structures of geometric spaces. Develops expertise in abstract mathematics and theoretical research. Focuses on advanced mathematical concepts. Graduates work in academia, research, and higher education.</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="n"/>
+      <c r="H68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Geospatial Analytics</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000068</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Studies advanced analysis of geographic and spatial data. Develops expertise in GIS, machine learning, and predictive modeling. Focuses on spatial decision-making. Graduates work in academia, government, and technology industries.</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="n"/>
+      <c r="H69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Grain Science</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000069</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Agricultural Science</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Studies grain production, processing, and quality. Develops expertise in cereal chemistry and agricultural research. Focuses on food quality and sustainable production. Graduates work in academia, agriculture, and food industries.</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="n"/>
+      <c r="H70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Health Economics and Policy</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000070</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Health Economics</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Integrates economic analysis with healthcare policy research. Develops expertise in health financing and policy evaluation. Focuses on improving health systems. Graduates work in academia, government, and healthcare organizations.</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Hispanic Studies and Comparative Literature</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000071</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Literature</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Combines Hispanic studies with comparative literary research. Develops expertise in literary analysis and cross-cultural interpretation. Focuses on global literary traditions. Graduates work in academia, publishing, and education.</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="n"/>
+      <c r="H72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>PhD in History of Art and Archaeology</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000072</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Art History</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Combines art history with archaeological research. Develops expertise in material culture and historical interpretation. Focuses on ancient and historical artifacts. Graduates work in academia, museums, and heritage organizations.</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Laser, Photonics and Vision</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000073</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Studies laser systems, photonics, and optical vision technologies. Develops expertise in optics, imaging, and applied physics. Focuses on light-based technologies. Graduates work in academia, research labs, and optical industries.</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="n"/>
+      <c r="H74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Latin American Cultural Studies</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000074</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Cultural Studies</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Explores cultural production, identity, and history in Latin America. Develops expertise in literary and cultural theory. Focuses on regional cultural expression. Graduates work in academia, publishing, and cultural organizations.</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="n"/>
+      <c r="H75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Leadership and Policy Studies in Education</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000075</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Examines leadership and policy in educational systems. Develops expertise in administration, policy analysis, and school leadership. Focuses on educational improvement. Graduates work in academia, schools, and government agencies.</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Management Finance</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000076</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Integrates financial management with organizational strategy. Develops expertise in corporate finance, investment, and risk management. Focuses on financial decision-making. Graduates work in finance, corporations, and consulting.</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="n"/>
+      <c r="H77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Marine Engine Engineering</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000077</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Marine Engineering</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Focuses on design and maintenance of marine propulsion systems. Develops expertise in mechanical and marine systems engineering. Focuses on ship engine performance. Graduates work in shipping, engineering, and maritime industries.</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Marketing and Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000078</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Studies marketing strategies for new ventures and startups. Develops expertise in innovation, branding, and business development. Focuses on entrepreneurial growth. Graduates work in startups, consulting, and business development.</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="n"/>
+      <c r="H79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>PhD in Phonetics and Phonology</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000079</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Linguistics</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Combines speech sound analysis with language sound systems. Develops expertise in linguistic theory and speech research. Focuses on sound structure and communication. Graduates work in academia, linguistics, and speech technology.</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="n"/>
+      <c r="H80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Applied Science in Nursing and Allied Health</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000080</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Nursing and Allied Health</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Studies basic nursing and healthcare support. Develops clinical and patient care skills. Focuses on healthcare services. Prepares graduates for healthcare support roles.</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="n"/>
+      <c r="H81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Applied Science in Medical Assistant</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000081</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Medical Assistance</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Studies clinical and administrative healthcare support. Develops patient care skills. Focuses on medical office practice. Prepares graduates for healthcare support roles.</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="n"/>
+      <c r="H82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Science in Radiography</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000082</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Radiography</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Studies medical imaging and radiographic techniques. Develops imaging, patient care, and technical skills. Focuses on diagnostic imaging procedures. Graduates work in hospitals and medical imaging departments.</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="n"/>
+      <c r="H83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Arts in Marketing</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000083</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Studies marketing strategies and consumer behavior. Develops communication, analytical, and promotional skills. Focuses on branding, advertising, and market research. Graduates work in marketing, sales, and retail.</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Applied Science in Dental Hygiene</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000084</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Dental Hygiene</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Studies preventive dental care and oral health. Develops clinical, patient care, and communication skills. Focuses on dental hygiene procedures and education. Graduates work in dental clinics and healthcare facilities.</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="n"/>
+      <c r="H85" s="6" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Applied Science in Radiography</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000085</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Radiography</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Studies diagnostic imaging and radiographic procedures. Develops imaging, patient care, and technical skills. Focuses on producing medical images for diagnosis. Graduates work in hospitals and diagnostic imaging centers.</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="n"/>
+      <c r="H86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Applied Science in Diagnostic Medical Sonography</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000086</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Diagnostic Medical Sonography</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Studies ultrasound imaging and patient care. Develops diagnostic imaging, technical, and clinical skills. Focuses on safe and accurate medical sonography. Prepares graduates for careers as diagnostic medical sonographers.</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="n"/>
+      <c r="H87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Science in Music Production</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000087</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Music Production</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Studies audio recording, music technology, and production. Develops recording, editing, and sound design skills. Focuses on creating professional music productions. Graduates work in recording studios and media production.</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="n"/>
+      <c r="H88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Applied Science</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000088</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Applied Science</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Studies practical scientific and technical applications. Develops laboratory, technical, and problem-solving skills. Focuses on career-ready scientific knowledge. Graduates work in technical, healthcare, and industrial roles.</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="n"/>
+      <c r="H89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Science in Nursing</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000089</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Studies nursing science and patient-centered care. Develops clinical, communication, and healthcare skills. Focuses on safe nursing practice and health promotion. Graduates work in hospitals, clinics, and healthcare facilities.</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="n"/>
+      <c r="H90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Arts</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000090</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Studies humanities, social sciences, and communication. Develops critical thinking, writing, and analytical skills. Focuses on broad academic preparation. Graduates continue higher education or enter diverse professional fields.</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="n"/>
+      <c r="H91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Arts Degree</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000091</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Studies a broad range of humanities and social sciences. Develops communication, research, and critical thinking skills. Focuses on transferable academic knowledge. Graduates continue higher education or pursue entry-level careers.</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="n"/>
+      <c r="H92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Nursing</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000092</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Studies patient care and foundational nursing practice. Develops clinical, communication, and healthcare skills. Focuses on evidence-based nursing and patient safety. Graduates work in hospitals, clinics, and healthcare facilities.</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="n"/>
+      <c r="H93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Science in Business</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000093</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Studies core business principles and organizational practices. Develops communication, management, and analytical skills. Focuses on finance, marketing, and operations. Graduates work in business support, retail, and administration.</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="n"/>
+      <c r="H94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Science</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000094</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Studies foundational scientific concepts and methods. Develops laboratory, analytical, and problem-solving skills. Focuses on biology, chemistry, and scientific inquiry. Graduates continue science studies or work in technical fields.</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="n"/>
+      <c r="H95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Science in Business Administration</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000095</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Business Administration</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Studies business operations and management fundamentals. Develops organizational, communication, and leadership skills. Focuses on business strategy and workplace effectiveness. Graduates work in administration, sales, and operations.</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="n"/>
+      <c r="H96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Science in Biology and Ecology</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000096</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Biology and Ecology</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>Studies biological systems and ecological processes. Develops laboratory, fieldwork, and analytical skills. Focuses on ecosystems, biodiversity, and environmental science. Graduates work in environmental organizations and laboratories.</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="n"/>
+      <c r="H97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Applied Science in Accounting</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000097</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>Studies accounting principles and financial reporting. Develops bookkeeping, financial analysis, and accounting software skills. Focuses on business finance and compliance. Graduates work in accounting, bookkeeping, and finance support.</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="n"/>
+      <c r="H98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Applied Science in Hospitality Management</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000098</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Hospitality Management</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>Studies hospitality operations and customer service management. Develops leadership, communication, and operational skills. Focuses on hotels, tourism, and guest satisfaction. Graduates work in hospitality, tourism, and hotel management.</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="n"/>
+      <c r="H99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Science in Computer Science</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000099</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>Studies computing principles and software development. Develops programming, analytical, and technical problem-solving skills. Focuses on algorithms, databases, and computer systems. Graduates work in IT support and software development.</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="n"/>
+      <c r="H100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>Associate of Arts in Business Administration</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>DEG-000100</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Business Administration</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>Studies business operations and organizational management. Develops leadership, communication, and administrative skills. Focuses on finance, marketing, and business practices. Graduates work in administration, retail, and business support.</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="n"/>
+      <c r="H101" s="6" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>

--- a/apps/api/data/excel_templates/degrees.xlsx
+++ b/apps/api/data/excel_templates/degrees.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -70,9 +70,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,3204 +491,3004 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Master in Philosophy and English Literature</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>DEG-000001</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Literature &amp; Philosophy</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Focuses on literary and philosophical texts. Develops analytical and interpretive skills. Studies cultural theory. Emphasises critical reading. Prepares for academic careers.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Master in Philosophy and Mathematics</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>DEG-000002</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Mathematical Philosophy</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Focuses on logic and mathematical reasoning. Develops analytical and abstract thinking. Studies formal systems. Emphasises theoretical inquiry. Prepares for research careers.</t>
         </is>
       </c>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Master in Philosophy and Public Policy</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>DEG-000003</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Policy Studies</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Focuses on ethical foundations of policy-making. Develops analytical and governance skills. Studies public systems. Emphasises decision frameworks. Prepares for policy roles.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Master in Philosophy and Religion</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>DEG-000004</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Religious Studies</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Focuses on philosophical analysis of religion. Develops interpretive and critical skills. Studies belief systems. Emphasises theological inquiry. Prepares for academic roles.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Master in Photonics</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>DEG-000005</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Physics &amp; Engineering</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Focuses on light manipulation and optical systems. Develops experimental and theoretical skills. Studies wave optics. Emphasises applied physics. Prepares for research roles.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Master in Photonics and Quantum Sciences</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>DEG-000006</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Quantum Technology</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Focuses on quantum optics and photonics. Develops theoretical and experimental skills. Studies quantum systems. Emphasises advanced research. Prepares for scientific careers.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Master in Physical Sciences</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>DEG-000007</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Natural Sciences</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Focuses on physics and related sciences. Develops analytical and experimental skills. Studies matter and energy. Emphasises research methods. Prepares for scientific careers.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Master in Physical Therapy and Rehabilitation</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>DEG-000008</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Rehabilitation Science</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Focuses on restoring physical function after injury. Develops therapeutic skills. Studies movement recovery. Emphasises clinical rehabilitation. Prepares for therapy careers.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Master in Physics and Technology of Nanostructures</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>DEG-000009</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Nanotechnology</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Focuses on engineered nanoscale structures. Develops experimental and fabrication skills. Studies quantum effects. Emphasises advanced materials. Prepares for research roles.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Master in Physics and Thermal Physics of Innovative Nuclear Power Installations</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>DEG-000010</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Focuses on thermal and reactor physics. Develops modelling and engineering skills. Studies nuclear systems. Emphasises energy innovation. Prepares for nuclear industry roles.</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Master in Physics of Complex Systems and Biophysics</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>DEG-000011</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Biophysics</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Focuses on complex systems in biology and physics. Develops analytical skills. Studies living systems. Emphasises interdisciplinary research. Prepares for scientific careers.</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Master in Physics with Mathematics</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>DEG-000012</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Mathematical Physics</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Focuses on mathematical methods in physics. Develops modelling and analytical skills. Studies theoretical frameworks. Emphasises problem-solving. Prepares for research roles.</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Master in Physics with Planetary and Space Physics</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>DEG-000013</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Space Physics</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Focuses on planetary systems and space environments. Develops analytical skills. Studies solar and planetary physics. Emphasises space science. Prepares for research careers.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Master in Planning and Management of Tourism Systems</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>DEG-000014</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Tourism Management</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Focuses on tourism system design and management. Develops planning and business skills. Studies tourism flows. Emphasises sustainability. Prepares for tourism industry roles.</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Master in Plasma Physics, Spectroscopy and Self-Organization</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>DEG-000015</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Applied Physics</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Focuses on plasma diagnostics and systems behaviour. Develops analytical skills. Studies light-matter interaction. Emphasises advanced research. Prepares for physics careers.</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Master in Play Therapy</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>DEG-000016</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Psychotherapy</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Focuses on therapeutic use of play for children. Develops counselling skills. Studies child psychology. Emphasises emotional development. Prepares for clinical therapy roles.</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Master in Podiatric Surgery</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>DEG-000017</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Surgical Medicine</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Focuses on surgical treatment of foot disorders. Develops clinical and surgical skills. Studies anatomy and pathology. Emphasises operative care. Prepares for surgical roles.</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Master in Portuguese and Business</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>DEG-000018</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Business Communication</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Focuses on Portuguese language in business contexts. Develops communication skills. Studies commerce and culture. Emphasises international trade. Prepares for business roles.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Master in Post-production with Sound Design</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>DEG-000019</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Media Production</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Focuses on audio post-production for media. Develops technical and creative skills. Studies sound design. Emphasises film and media industries. Prepares for production roles.</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Master in Power, Electronic and Telecommunication Engineering</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>DEG-000020</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Electrical Engineering</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Focuses on integrated power and communication systems. Develops technical skills. Studies networks and electronics. Emphasises infrastructure. Prepares for engineering roles.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Master in Process Engineering</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>DEG-000021</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Chemical/Industrial Engineering</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Focuses on industrial process design and optimisation. Develops engineering skills. Studies production systems. Emphasises efficiency and safety. Prepares for industry roles.</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Master in Professional Archaeology and Comprehensive Heritage Management</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>DEG-000022</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Archaeology</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Focuses on archaeological practice and heritage management. Develops field skills. Studies cultural preservation. Emphasises applied archaeology. Prepares for heritage roles.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Master in Professional Non-surgical Aesthetic Practice</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>DEG-000023</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Aesthetic Medicine</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Focuses on cosmetic non-surgical treatments. Develops clinical and procedural skills. Studies skin aesthetics. Emphasises patient care. Prepares for aesthetic practice roles.</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Master in Professional Studies in Education</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>DEG-000024</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Focuses on advanced teaching and learning practice. Develops pedagogical skills. Studies education systems. Emphasises instructional improvement. Prepares for educator roles.</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Master in Professional Translation Studies</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>DEG-000025</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Translation Studies</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Focuses on advanced translation theory and practice. Develops language skills. Studies translation techniques. Emphasises accuracy and fluency. Prepares for translator roles.</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Master in Prostate Cancer Care</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>DEG-000026</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Oncology</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Focuses on diagnosis and treatment of prostate cancer. Develops clinical skills. Studies oncology care pathways. Emphasises patient management. Prepares for healthcare roles.</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Master in Psychology Conversion</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>DEG-000027</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Conversion Psychology</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Focuses on foundational psychology training. Develops core analytical skills. Studies psychological theory. Emphasises transition into field. Prepares for psychology careers.</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Master in Psycho-oncology and Palliative Care</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>DEG-000028</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Health Psychology</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Focuses on psychological support in cancer care. Develops clinical intervention skills. Studies patient wellbeing. Emphasises end-of-life care. Prepares for healthcare roles.</t>
         </is>
       </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Master in Public Health, Public Health Nutrition and Epidemiology</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>DEG-000029</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Public Health Nutrition</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Focuses on nutrition and disease prevention. Develops epidemiological skills. Studies diet and population health. Emphasises prevention strategies. Prepares for health roles.</t>
         </is>
       </c>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Bachelor of Design in Visual Communication and BA in International Studies</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>DEG-000030</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Design / Communication</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Combines visual communication with global studies. Covers branding and media. Develops creative skills. Prepares for design careers.</t>
         </is>
       </c>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Bachelor of Teaching and BA in Mathematics</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>DEG-000031</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Education / Mathematics</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Combines teaching with mathematics. Covers pedagogy and quantitative skills. Develops instructional ability. Prepares for teaching roles.</t>
         </is>
       </c>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Bachelor of Health Science in Traditional Chinese Medicine and BA in International Studies</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>DEG-000032</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Health / Traditional Medicine</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" t="n">
         <v>4</v>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Combines Chinese medicine with global studies. Covers holistic health systems. Develops clinical knowledge. Prepares for healthcare roles.</t>
         </is>
       </c>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Bachelor of Teaching and BA in Visual Arts</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>DEG-000033</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Education / Arts</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" t="n">
         <v>4</v>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Combines teaching with visual arts practice. Covers pedagogy and creativity. Develops instructional skills. Prepares for arts education roles.</t>
         </is>
       </c>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Bachelor of Education and BA in International Studies</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>DEG-000034</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" t="n">
         <v>4</v>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Combines teaching qualifications with global studies. Covers pedagogy and culture. Develops instructional skills. Prepares for education roles.</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Bachelor of Teaching and BA in Technology</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>DEG-000035</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Education / Technology</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" t="n">
         <v>4</v>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Combines teaching with technology studies. Covers digital tools and pedagogy. Develops instructional skills. Prepares for STEM education roles.</t>
         </is>
       </c>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="6" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Bachelor of Journalism and Professional Writing and BA in Creative Writing and Literature</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>DEG-000036</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Journalism / Writing</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" t="n">
         <v>4</v>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Combines journalism with creative writing. Covers reporting, storytelling, and media. Develops communication skills. Prepares for media careers.</t>
         </is>
       </c>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Bachelor of Commerce, BA in Psychology</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>DEG-000037</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Business / Psychology</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" t="n">
         <v>4</v>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Combines commerce with psychology studies. Covers business strategy and human behaviour. Develops analytical skills. Prepares for corporate roles.</t>
         </is>
       </c>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Bachelor of Nursing and BA in International Studies</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>DEG-000038</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Nursing</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" t="n">
         <v>4</v>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Combines nursing practice with global studies. Covers healthcare systems and patient care. Develops clinical skills. Prepares for nursing careers.</t>
         </is>
       </c>
-      <c r="G39" s="6" t="n"/>
-      <c r="H39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Bachelor of Teaching and BA in Humanities</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>DEG-000039</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" t="n">
         <v>4</v>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Combines teaching qualification with humanities studies. Covers pedagogy and culture. Develops instructional skills. Prepares for education roles.</t>
         </is>
       </c>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="6" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Bachelor of Design in Interior Architecture and BA in International Studies</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>DEG-000040</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Design / Architecture</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" t="n">
         <v>4</v>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Combines interior design with global studies. Covers spatial design and culture. Develops creative and technical skills. Prepares for design careers.</t>
         </is>
       </c>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Bachelor of Design in Product Design and BA in International Studies</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>DEG-000041</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Design / Product</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Combines product design with global studies. Covers innovation and user-centred design. Develops technical skills. Prepares for design industry roles.</t>
         </is>
       </c>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Bachelor of Medical Science and BA in International Studies</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>DEG-000042</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Medical Science</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" t="n">
         <v>4</v>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Combines medical science with global studies. Covers biology, health systems, and policy. Develops scientific skills. Prepares for health sector roles.</t>
         </is>
       </c>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Bachelor of Design in Animation and BA in International Studies</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>DEG-000043</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Design / International Studies</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" t="n">
         <v>4</v>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Combines animation with global cultural studies. Covers storytelling and media production. Develops creative skills. Prepares for animation and media roles.</t>
         </is>
       </c>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Bachelor of Design in Photography and BA in International Studies</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>DEG-000044</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Design / Photography</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" t="n">
         <v>4</v>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Combines photography with international studies. Covers visual storytelling and culture. Develops artistic skills. Prepares for media and photography roles.</t>
         </is>
       </c>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="6" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Bachelor of Commerce and BA in Psychology and Economics</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>DEG-000045</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Business / Social Science</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Integrates commerce, psychology, and economics. Covers markets, behaviour, and policy. Develops analytical skills. Prepares for finance and consulting roles.</t>
         </is>
       </c>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Bachelor of Communication in Creative Writing and BA in International Studies</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>DEG-000046</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Communication / International Studies</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" t="n">
         <v>4</v>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Combines creative writing with global studies. Covers media, culture, and communication. Develops storytelling skills. Prepares for media and international roles.</t>
         </is>
       </c>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="6" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Bachelor of Construction Project Management, BA in International Studies</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>DEG-000047</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Construction / International Studies</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" t="n">
         <v>4</v>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Combines construction management with global studies. Covers planning, infrastructure, and policy. Develops leadership skills. Prepares for project management roles.</t>
         </is>
       </c>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Bachelor of Commerce and BA in Psychology</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>DEG-000048</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Business / Psychology</t>
         </is>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Combines business commerce with psychological science. Covers markets, behaviour, and analytics. Develops interdisciplinary skills. Prepares for business and HR roles.</t>
         </is>
       </c>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Bachelor in Transfer Degree</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>DEG-000049</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>General Studies</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" t="n">
         <v>4</v>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Provides foundational academic coursework for transfer. Develops core academic skills. Focuses on university progression pathways. Prepares students for advanced degrees.</t>
         </is>
       </c>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Bachelor and MBA in Supply Chain Management</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>DEG-000050</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Business / Logistics</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" t="n">
         <v>4</v>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Integrated program covering supply chain and advanced business management. Covers logistics, operations, and strategy. Develops leadership skills. Prepares for senior management roles.</t>
         </is>
       </c>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Bachelor of Law with English Language Studies</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>DEG-000051</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>English Studies</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" t="n">
         <v>4</v>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Combines law with advanced study of English linguistics and usage. Builds strong written and verbal reasoning. Prepares for careers in law, media, publishing, or public administration.</t>
         </is>
       </c>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Bachelor of Law with English</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>DEG-000052</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="E53" t="n">
         <v>4</v>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Combines law with English language and literature studies. Strengthens critical thinking, analysis, and communication. Prepares for careers in law, publishing, education, or media industries.</t>
         </is>
       </c>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Bachelor of Law with Classical Studies</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>DEG-000053</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Classical Studies</t>
         </is>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E54" t="n">
         <v>4</v>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Integrates law with ancient Greek and Roman civilizations. Develops analytical and historical interpretation skills. Prepares for careers in law, academia, heritage, or cultural policy sectors.</t>
         </is>
       </c>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="6" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Bachelor of Law with Criminology</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>DEG-000054</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Criminology</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" t="n">
         <v>4</v>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Combines law with the study of crime, justice, and society. Develops understanding of criminal behavior and legal responses. Leads to careers in policing, legal practice, or criminal justice policy.</t>
         </is>
       </c>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="6" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Bachelor of Forestry Transfer</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>DEG-000055</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Forestry (Transfer Program)</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" t="n">
         <v>4</v>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Provides foundational forestry education for academic transfer pathways. Develops basic ecological and scientific skills. Prepares students for advanced forestry studies. Strengthens academic readiness. Supports progression into specialized forestry degrees.</t>
         </is>
       </c>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="6" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Bachelor of Language and Literature Education</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>DEG-000056</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Education &amp; Language</t>
         </is>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" t="n">
         <v>4</v>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Focuses on teaching languages and literature. Builds pedagogy and communication skills. Graduates work as language teachers.</t>
         </is>
       </c>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="6" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Bachelor of Mathematics with Education</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>DEG-000057</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Mathematics Education</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="E58" t="n">
         <v>4</v>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Focuses on mathematics teaching and learning methods. Builds pedagogical skills. Graduates work in schools or education roles.</t>
         </is>
       </c>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Bachelor of Italian and Persian</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>DEG-000058</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Language Studies</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" t="n">
         <v>4</v>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Combines Italian and Persian languages. Builds intercultural communication skills. Graduates work in translation and diplomacy.</t>
         </is>
       </c>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Bachelor of Medical Studies and Doctor of Medicine</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>DEG-000059</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Medical Pathway</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E60" t="n">
         <v>4</v>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Integrated medical training program. Builds clinical and scientific expertise. Graduates become licensed medical practitioners.</t>
         </is>
       </c>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Bachelor of History Teaching</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>DEG-000060</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E61" t="n">
         <v>4</v>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Studies methods of teaching history. Develops pedagogical skills. Focuses on classroom instruction. Graduates work as educators.</t>
         </is>
       </c>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="6" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>PhD in Fluids Engineering</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>DEG-000061</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" t="n">
         <v>3</v>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Studies fluid flow and engineering system design. Develops expertise in computational modeling and experimental research. Focuses on industrial and energy applications. Graduates work in research, aerospace, and engineering firms.</t>
         </is>
       </c>
-      <c r="G62" s="6" t="n"/>
-      <c r="H62" s="6" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>PhD in Food and Biochemical Technology</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>DEG-000062</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Food Science</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E63" t="n">
         <v>3</v>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Combines food science with biochemical technologies. Develops expertise in food processing and biochemical research. Focuses on improving food quality and innovation. Graduates work in academia, biotechnology, and food industries.</t>
         </is>
       </c>
-      <c r="G63" s="6" t="n"/>
-      <c r="H63" s="6" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>PhD in Food Systems</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>DEG-000063</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Food Systems</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" t="n">
         <v>3</v>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Explores food production, distribution, and consumption systems. Develops interdisciplinary research and policy skills. Focuses on sustainability and resilience. Graduates work in academia, government, and nonprofit organizations.</t>
         </is>
       </c>
-      <c r="G64" s="6" t="n"/>
-      <c r="H64" s="6" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>PhD in Gender Studies</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>DEG-000064</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Gender Studies</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" t="n">
         <v>3</v>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Explores gender through social, political, and cultural research. Develops critical thinking and interdisciplinary research skills. Focuses on identity and equality. Graduates work in academia, policy, and community organizations.</t>
         </is>
       </c>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="6" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>PhD in Geodesy and Geoinformatics</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>DEG-000065</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Geospatial Science</t>
         </is>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" t="n">
         <v>3</v>
       </c>
-      <c r="F66" s="6" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Combines geodesy with digital geographic information systems. Develops expertise in spatial analysis and geospatial technologies. Focuses on Earth measurement and mapping. Graduates work in academia, surveying, and GIS industries.</t>
         </is>
       </c>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>PhD in Geography and Earth Science</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>DEG-000066</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Earth Science</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E67" t="n">
         <v>3</v>
       </c>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Combines geography with Earth science research. Develops expertise in environmental systems and geospatial analysis. Focuses on understanding Earth's processes. Graduates work in academia, environmental consulting, and government.</t>
         </is>
       </c>
-      <c r="G67" s="6" t="n"/>
-      <c r="H67" s="6" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>PhD in Geometry and Topology</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>DEG-000067</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" t="n">
         <v>3</v>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Studies the properties and structures of geometric spaces. Develops expertise in abstract mathematics and theoretical research. Focuses on advanced mathematical concepts. Graduates work in academia, research, and higher education.</t>
         </is>
       </c>
-      <c r="G68" s="6" t="n"/>
-      <c r="H68" s="6" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>PhD in Geospatial Analytics</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>DEG-000068</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Data Science</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E69" t="n">
         <v>3</v>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Studies advanced analysis of geographic and spatial data. Develops expertise in GIS, machine learning, and predictive modeling. Focuses on spatial decision-making. Graduates work in academia, government, and technology industries.</t>
         </is>
       </c>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="6" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>PhD in Grain Science</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>DEG-000069</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Agricultural Science</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E70" t="n">
         <v>3</v>
       </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Studies grain production, processing, and quality. Develops expertise in cereal chemistry and agricultural research. Focuses on food quality and sustainable production. Graduates work in academia, agriculture, and food industries.</t>
         </is>
       </c>
-      <c r="G70" s="6" t="n"/>
-      <c r="H70" s="6" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>PhD in Health Economics and Policy</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>DEG-000070</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Health Economics</t>
         </is>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E71" t="n">
         <v>3</v>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Integrates economic analysis with healthcare policy research. Develops expertise in health financing and policy evaluation. Focuses on improving health systems. Graduates work in academia, government, and healthcare organizations.</t>
         </is>
       </c>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="6" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>PhD in Hispanic Studies and Comparative Literature</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>DEG-000071</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" t="n">
         <v>3</v>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Combines Hispanic studies with comparative literary research. Develops expertise in literary analysis and cross-cultural interpretation. Focuses on global literary traditions. Graduates work in academia, publishing, and education.</t>
         </is>
       </c>
-      <c r="G72" s="6" t="n"/>
-      <c r="H72" s="6" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>PhD in History of Art and Archaeology</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>DEG-000072</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Art History</t>
         </is>
       </c>
-      <c r="E73" s="6" t="n">
+      <c r="E73" t="n">
         <v>3</v>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Combines art history with archaeological research. Develops expertise in material culture and historical interpretation. Focuses on ancient and historical artifacts. Graduates work in academia, museums, and heritage organizations.</t>
         </is>
       </c>
-      <c r="G73" s="6" t="n"/>
-      <c r="H73" s="6" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>PhD in Laser, Photonics and Vision</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>DEG-000073</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E74" t="n">
         <v>3</v>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Studies laser systems, photonics, and optical vision technologies. Develops expertise in optics, imaging, and applied physics. Focuses on light-based technologies. Graduates work in academia, research labs, and optical industries.</t>
         </is>
       </c>
-      <c r="G74" s="6" t="n"/>
-      <c r="H74" s="6" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>PhD in Latin American Cultural Studies</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>DEG-000074</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Cultural Studies</t>
         </is>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E75" t="n">
         <v>3</v>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Explores cultural production, identity, and history in Latin America. Develops expertise in literary and cultural theory. Focuses on regional cultural expression. Graduates work in academia, publishing, and cultural organizations.</t>
         </is>
       </c>
-      <c r="G75" s="6" t="n"/>
-      <c r="H75" s="6" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>PhD in Leadership and Policy Studies in Education</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>DEG-000075</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="E76" t="n">
         <v>3</v>
       </c>
-      <c r="F76" s="6" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Examines leadership and policy in educational systems. Develops expertise in administration, policy analysis, and school leadership. Focuses on educational improvement. Graduates work in academia, schools, and government agencies.</t>
         </is>
       </c>
-      <c r="G76" s="6" t="n"/>
-      <c r="H76" s="6" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>PhD in Management Finance</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>DEG-000076</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E77" t="n">
         <v>3</v>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Integrates financial management with organizational strategy. Develops expertise in corporate finance, investment, and risk management. Focuses on financial decision-making. Graduates work in finance, corporations, and consulting.</t>
         </is>
       </c>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="6" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>PhD in Marine Engine Engineering</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>DEG-000077</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Marine Engineering</t>
         </is>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E78" t="n">
         <v>3</v>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Focuses on design and maintenance of marine propulsion systems. Develops expertise in mechanical and marine systems engineering. Focuses on ship engine performance. Graduates work in shipping, engineering, and maritime industries.</t>
         </is>
       </c>
-      <c r="G78" s="6" t="n"/>
-      <c r="H78" s="6" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>PhD in Marketing and Entrepreneurship</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>DEG-000078</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="E79" t="n">
         <v>3</v>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Studies marketing strategies for new ventures and startups. Develops expertise in innovation, branding, and business development. Focuses on entrepreneurial growth. Graduates work in startups, consulting, and business development.</t>
         </is>
       </c>
-      <c r="G79" s="6" t="n"/>
-      <c r="H79" s="6" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>PhD in Phonetics and Phonology</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>DEG-000079</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Linguistics</t>
         </is>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E80" t="n">
         <v>3</v>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Combines speech sound analysis with language sound systems. Develops expertise in linguistic theory and speech research. Focuses on sound structure and communication. Graduates work in academia, linguistics, and speech technology.</t>
         </is>
       </c>
-      <c r="G80" s="6" t="n"/>
-      <c r="H80" s="6" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Nursing and Allied Health</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>DEG-000080</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Nursing and Allied Health</t>
         </is>
       </c>
-      <c r="E81" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="E81" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Studies basic nursing and healthcare support. Develops clinical and patient care skills. Focuses on healthcare services. Prepares graduates for healthcare support roles.</t>
         </is>
       </c>
-      <c r="G81" s="6" t="n"/>
-      <c r="H81" s="6" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Medical Assistant</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>DEG-000081</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Medical Assistance</t>
         </is>
       </c>
-      <c r="E82" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Studies clinical and administrative healthcare support. Develops patient care skills. Focuses on medical office practice. Prepares graduates for healthcare support roles.</t>
         </is>
       </c>
-      <c r="G82" s="6" t="n"/>
-      <c r="H82" s="6" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Associate of Science in Radiography</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>DEG-000082</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Radiography</t>
         </is>
       </c>
-      <c r="E83" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Studies medical imaging and radiographic techniques. Develops imaging, patient care, and technical skills. Focuses on diagnostic imaging procedures. Graduates work in hospitals and medical imaging departments.</t>
         </is>
       </c>
-      <c r="G83" s="6" t="n"/>
-      <c r="H83" s="6" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Associate of Arts in Marketing</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>DEG-000083</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="E84" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="E84" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Studies marketing strategies and consumer behavior. Develops communication, analytical, and promotional skills. Focuses on branding, advertising, and market research. Graduates work in marketing, sales, and retail.</t>
         </is>
       </c>
-      <c r="G84" s="6" t="n"/>
-      <c r="H84" s="6" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Dental Hygiene</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>DEG-000084</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Dental Hygiene</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="E85" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Studies preventive dental care and oral health. Develops clinical, patient care, and communication skills. Focuses on dental hygiene procedures and education. Graduates work in dental clinics and healthcare facilities.</t>
         </is>
       </c>
-      <c r="G85" s="6" t="n"/>
-      <c r="H85" s="6" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Radiography</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>DEG-000085</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Radiography</t>
         </is>
       </c>
-      <c r="E86" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="E86" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Studies diagnostic imaging and radiographic procedures. Develops imaging, patient care, and technical skills. Focuses on producing medical images for diagnosis. Graduates work in hospitals and diagnostic imaging centers.</t>
         </is>
       </c>
-      <c r="G86" s="6" t="n"/>
-      <c r="H86" s="6" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Diagnostic Medical Sonography</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>DEG-000086</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Diagnostic Medical Sonography</t>
         </is>
       </c>
-      <c r="E87" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="E87" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>Studies ultrasound imaging and patient care. Develops diagnostic imaging, technical, and clinical skills. Focuses on safe and accurate medical sonography. Prepares graduates for careers as diagnostic medical sonographers.</t>
         </is>
       </c>
-      <c r="G87" s="6" t="n"/>
-      <c r="H87" s="6" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>Associate of Science in Music Production</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>DEG-000087</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Music Production</t>
         </is>
       </c>
-      <c r="E88" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="E88" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Studies audio recording, music technology, and production. Develops recording, editing, and sound design skills. Focuses on creating professional music productions. Graduates work in recording studios and media production.</t>
         </is>
       </c>
-      <c r="G88" s="6" t="n"/>
-      <c r="H88" s="6" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Associate of Applied Science</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>DEG-000088</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Applied Science</t>
         </is>
       </c>
-      <c r="E89" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="E89" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Studies practical scientific and technical applications. Develops laboratory, technical, and problem-solving skills. Focuses on career-ready scientific knowledge. Graduates work in technical, healthcare, and industrial roles.</t>
         </is>
       </c>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="6" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Associate of Science in Nursing</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>DEG-000089</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Nursing</t>
         </is>
       </c>
-      <c r="E90" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Studies nursing science and patient-centered care. Develops clinical, communication, and healthcare skills. Focuses on safe nursing practice and health promotion. Graduates work in hospitals, clinics, and healthcare facilities.</t>
         </is>
       </c>
-      <c r="G90" s="6" t="n"/>
-      <c r="H90" s="6" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Associate of Arts</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>DEG-000090</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="E91" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="E91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Studies humanities, social sciences, and communication. Develops critical thinking, writing, and analytical skills. Focuses on broad academic preparation. Graduates continue higher education or enter diverse professional fields.</t>
         </is>
       </c>
-      <c r="G91" s="6" t="n"/>
-      <c r="H91" s="6" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Associate of Arts Degree</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>DEG-000091</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="E92" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="E92" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Studies a broad range of humanities and social sciences. Develops communication, research, and critical thinking skills. Focuses on transferable academic knowledge. Graduates continue higher education or pursue entry-level careers.</t>
         </is>
       </c>
-      <c r="G92" s="6" t="n"/>
-      <c r="H92" s="6" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Associate of Nursing</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>DEG-000092</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Nursing</t>
         </is>
       </c>
-      <c r="E93" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="E93" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Studies patient care and foundational nursing practice. Develops clinical, communication, and healthcare skills. Focuses on evidence-based nursing and patient safety. Graduates work in hospitals, clinics, and healthcare facilities.</t>
         </is>
       </c>
-      <c r="G93" s="6" t="n"/>
-      <c r="H93" s="6" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Associate of Science in Business</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>DEG-000093</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="E94" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>Studies core business principles and organizational practices. Develops communication, management, and analytical skills. Focuses on finance, marketing, and operations. Graduates work in business support, retail, and administration.</t>
         </is>
       </c>
-      <c r="G94" s="6" t="n"/>
-      <c r="H94" s="6" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>Associate of Science</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>DEG-000094</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="E95" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>Studies foundational scientific concepts and methods. Develops laboratory, analytical, and problem-solving skills. Focuses on biology, chemistry, and scientific inquiry. Graduates continue science studies or work in technical fields.</t>
         </is>
       </c>
-      <c r="G95" s="6" t="n"/>
-      <c r="H95" s="6" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>Associate of Science in Business Administration</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>DEG-000095</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Business Administration</t>
         </is>
       </c>
-      <c r="E96" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Studies business operations and management fundamentals. Develops organizational, communication, and leadership skills. Focuses on business strategy and workplace effectiveness. Graduates work in administration, sales, and operations.</t>
         </is>
       </c>
-      <c r="G96" s="6" t="n"/>
-      <c r="H96" s="6" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>Associate of Science in Biology and Ecology</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>DEG-000096</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>Biology and Ecology</t>
         </is>
       </c>
-      <c r="E97" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Studies biological systems and ecological processes. Develops laboratory, fieldwork, and analytical skills. Focuses on ecosystems, biodiversity, and environmental science. Graduates work in environmental organizations and laboratories.</t>
         </is>
       </c>
-      <c r="G97" s="6" t="n"/>
-      <c r="H97" s="6" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Accounting</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>DEG-000097</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="E98" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Studies accounting principles and financial reporting. Develops bookkeeping, financial analysis, and accounting software skills. Focuses on business finance and compliance. Graduates work in accounting, bookkeeping, and finance support.</t>
         </is>
       </c>
-      <c r="G98" s="6" t="n"/>
-      <c r="H98" s="6" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Hospitality Management</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>DEG-000098</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Hospitality Management</t>
         </is>
       </c>
-      <c r="E99" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="E99" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Studies hospitality operations and customer service management. Develops leadership, communication, and operational skills. Focuses on hotels, tourism, and guest satisfaction. Graduates work in hospitality, tourism, and hotel management.</t>
         </is>
       </c>
-      <c r="G99" s="6" t="n"/>
-      <c r="H99" s="6" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>Associate of Science in Computer Science</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>DEG-000099</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="E100" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F100" s="6" t="inlineStr">
+      <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Studies computing principles and software development. Develops programming, analytical, and technical problem-solving skills. Focuses on algorithms, databases, and computer systems. Graduates work in IT support and software development.</t>
         </is>
       </c>
-      <c r="G100" s="6" t="n"/>
-      <c r="H100" s="6" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="6" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Associate of Arts in Business Administration</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>DEG-000100</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>Business Administration</t>
         </is>
       </c>
-      <c r="E101" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F101" s="6" t="inlineStr">
+      <c r="E101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Studies business operations and organizational management. Develops leadership, communication, and administrative skills. Focuses on finance, marketing, and business practices. Graduates work in administration, retail, and business support.</t>
         </is>
       </c>
-      <c r="G101" s="6" t="n"/>
-      <c r="H101" s="6" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>

--- a/apps/api/data/excel_templates/degrees.xlsx
+++ b/apps/api/data/excel_templates/degrees.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -70,6 +70,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,3004 +494,3204 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Master in Philosophy and English Literature</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>DEG-000001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Literature &amp; Philosophy</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Focuses on literary and philosophical texts. Develops analytical and interpretive skills. Studies cultural theory. Emphasises critical reading. Prepares for academic careers.</t>
         </is>
       </c>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Master in Philosophy and Mathematics</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>DEG-000002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Mathematical Philosophy</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Focuses on logic and mathematical reasoning. Develops analytical and abstract thinking. Studies formal systems. Emphasises theoretical inquiry. Prepares for research careers.</t>
         </is>
       </c>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Master in Philosophy and Public Policy</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>DEG-000003</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Policy Studies</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Focuses on ethical foundations of policy-making. Develops analytical and governance skills. Studies public systems. Emphasises decision frameworks. Prepares for policy roles.</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Master in Philosophy and Religion</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>DEG-000004</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Religious Studies</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Focuses on philosophical analysis of religion. Develops interpretive and critical skills. Studies belief systems. Emphasises theological inquiry. Prepares for academic roles.</t>
         </is>
       </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Master in Photonics</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>DEG-000005</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Physics &amp; Engineering</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Focuses on light manipulation and optical systems. Develops experimental and theoretical skills. Studies wave optics. Emphasises applied physics. Prepares for research roles.</t>
         </is>
       </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Master in Photonics and Quantum Sciences</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>DEG-000006</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Quantum Technology</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Focuses on quantum optics and photonics. Develops theoretical and experimental skills. Studies quantum systems. Emphasises advanced research. Prepares for scientific careers.</t>
         </is>
       </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Master in Physical Sciences</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>DEG-000007</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Natural Sciences</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Focuses on physics and related sciences. Develops analytical and experimental skills. Studies matter and energy. Emphasises research methods. Prepares for scientific careers.</t>
         </is>
       </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Master in Physical Therapy and Rehabilitation</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>DEG-000008</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Rehabilitation Science</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Focuses on restoring physical function after injury. Develops therapeutic skills. Studies movement recovery. Emphasises clinical rehabilitation. Prepares for therapy careers.</t>
         </is>
       </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Master in Physics and Technology of Nanostructures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>DEG-000009</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Nanotechnology</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Focuses on engineered nanoscale structures. Develops experimental and fabrication skills. Studies quantum effects. Emphasises advanced materials. Prepares for research roles.</t>
         </is>
       </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Master in Physics and Thermal Physics of Innovative Nuclear Power Installations</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>DEG-000010</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Focuses on thermal and reactor physics. Develops modelling and engineering skills. Studies nuclear systems. Emphasises energy innovation. Prepares for nuclear industry roles.</t>
         </is>
       </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Master in Physics of Complex Systems and Biophysics</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>DEG-000011</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Biophysics</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Focuses on complex systems in biology and physics. Develops analytical skills. Studies living systems. Emphasises interdisciplinary research. Prepares for scientific careers.</t>
         </is>
       </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Master in Physics with Mathematics</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>DEG-000012</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Mathematical Physics</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Focuses on mathematical methods in physics. Develops modelling and analytical skills. Studies theoretical frameworks. Emphasises problem-solving. Prepares for research roles.</t>
         </is>
       </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Master in Physics with Planetary and Space Physics</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>DEG-000013</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Space Physics</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Focuses on planetary systems and space environments. Develops analytical skills. Studies solar and planetary physics. Emphasises space science. Prepares for research careers.</t>
         </is>
       </c>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Master in Planning and Management of Tourism Systems</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>DEG-000014</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Tourism Management</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Focuses on tourism system design and management. Develops planning and business skills. Studies tourism flows. Emphasises sustainability. Prepares for tourism industry roles.</t>
         </is>
       </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Master in Plasma Physics, Spectroscopy and Self-Organization</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>DEG-000015</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Applied Physics</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Focuses on plasma diagnostics and systems behaviour. Develops analytical skills. Studies light-matter interaction. Emphasises advanced research. Prepares for physics careers.</t>
         </is>
       </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Master in Play Therapy</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>DEG-000016</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Psychotherapy</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Focuses on therapeutic use of play for children. Develops counselling skills. Studies child psychology. Emphasises emotional development. Prepares for clinical therapy roles.</t>
         </is>
       </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Master in Podiatric Surgery</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>DEG-000017</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Surgical Medicine</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="E18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Focuses on surgical treatment of foot disorders. Develops clinical and surgical skills. Studies anatomy and pathology. Emphasises operative care. Prepares for surgical roles.</t>
         </is>
       </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Master in Portuguese and Business</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>DEG-000018</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Business Communication</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Focuses on Portuguese language in business contexts. Develops communication skills. Studies commerce and culture. Emphasises international trade. Prepares for business roles.</t>
         </is>
       </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Master in Post-production with Sound Design</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>DEG-000019</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Media Production</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Focuses on audio post-production for media. Develops technical and creative skills. Studies sound design. Emphasises film and media industries. Prepares for production roles.</t>
         </is>
       </c>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Master in Power, Electronic and Telecommunication Engineering</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>DEG-000020</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Electrical Engineering</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Focuses on integrated power and communication systems. Develops technical skills. Studies networks and electronics. Emphasises infrastructure. Prepares for engineering roles.</t>
         </is>
       </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Master in Process Engineering</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>DEG-000021</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Chemical/Industrial Engineering</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Focuses on industrial process design and optimisation. Develops engineering skills. Studies production systems. Emphasises efficiency and safety. Prepares for industry roles.</t>
         </is>
       </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Master in Professional Archaeology and Comprehensive Heritage Management</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>DEG-000022</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Archaeology</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Focuses on archaeological practice and heritage management. Develops field skills. Studies cultural preservation. Emphasises applied archaeology. Prepares for heritage roles.</t>
         </is>
       </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Master in Professional Non-surgical Aesthetic Practice</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>DEG-000023</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Aesthetic Medicine</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Focuses on cosmetic non-surgical treatments. Develops clinical and procedural skills. Studies skin aesthetics. Emphasises patient care. Prepares for aesthetic practice roles.</t>
         </is>
       </c>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Master in Professional Studies in Education</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>DEG-000024</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>Focuses on advanced teaching and learning practice. Develops pedagogical skills. Studies education systems. Emphasises instructional improvement. Prepares for educator roles.</t>
         </is>
       </c>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Master in Professional Translation Studies</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>DEG-000025</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Translation Studies</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Focuses on advanced translation theory and practice. Develops language skills. Studies translation techniques. Emphasises accuracy and fluency. Prepares for translator roles.</t>
         </is>
       </c>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Master in Prostate Cancer Care</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>DEG-000026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Oncology</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="E27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Focuses on diagnosis and treatment of prostate cancer. Develops clinical skills. Studies oncology care pathways. Emphasises patient management. Prepares for healthcare roles.</t>
         </is>
       </c>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Master in Psychology Conversion</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>DEG-000027</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Conversion Psychology</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="E28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Focuses on foundational psychology training. Develops core analytical skills. Studies psychological theory. Emphasises transition into field. Prepares for psychology careers.</t>
         </is>
       </c>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Master in Psycho-oncology and Palliative Care</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>DEG-000028</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Health Psychology</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="E29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Focuses on psychological support in cancer care. Develops clinical intervention skills. Studies patient wellbeing. Emphasises end-of-life care. Prepares for healthcare roles.</t>
         </is>
       </c>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Master in Public Health, Public Health Nutrition and Epidemiology</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>DEG-000029</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Public Health Nutrition</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="E30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Focuses on nutrition and disease prevention. Develops epidemiological skills. Studies diet and population health. Emphasises prevention strategies. Prepares for health roles.</t>
         </is>
       </c>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Design in Visual Communication and BA in International Studies</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>DEG-000030</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Design / Communication</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>Combines visual communication with global studies. Covers branding and media. Develops creative skills. Prepares for design careers.</t>
         </is>
       </c>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Teaching and BA in Mathematics</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>DEG-000031</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Education / Mathematics</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Combines teaching with mathematics. Covers pedagogy and quantitative skills. Develops instructional ability. Prepares for teaching roles.</t>
         </is>
       </c>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Health Science in Traditional Chinese Medicine and BA in International Studies</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>DEG-000032</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>Health / Traditional Medicine</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>Combines Chinese medicine with global studies. Covers holistic health systems. Develops clinical knowledge. Prepares for healthcare roles.</t>
         </is>
       </c>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Teaching and BA in Visual Arts</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>DEG-000033</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>Education / Arts</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>Combines teaching with visual arts practice. Covers pedagogy and creativity. Develops instructional skills. Prepares for arts education roles.</t>
         </is>
       </c>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Education and BA in International Studies</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>DEG-000034</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Combines teaching qualifications with global studies. Covers pedagogy and culture. Develops instructional skills. Prepares for education roles.</t>
         </is>
       </c>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Teaching and BA in Technology</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>DEG-000035</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Education / Technology</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>Combines teaching with technology studies. Covers digital tools and pedagogy. Develops instructional skills. Prepares for STEM education roles.</t>
         </is>
       </c>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Journalism and Professional Writing and BA in Creative Writing and Literature</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>DEG-000036</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Journalism / Writing</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Combines journalism with creative writing. Covers reporting, storytelling, and media. Develops communication skills. Prepares for media careers.</t>
         </is>
       </c>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Commerce, BA in Psychology</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>DEG-000037</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Business / Psychology</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Combines commerce with psychology studies. Covers business strategy and human behaviour. Develops analytical skills. Prepares for corporate roles.</t>
         </is>
       </c>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Nursing and BA in International Studies</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>DEG-000038</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Nursing</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Combines nursing practice with global studies. Covers healthcare systems and patient care. Develops clinical skills. Prepares for nursing careers.</t>
         </is>
       </c>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Teaching and BA in Humanities</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>DEG-000039</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>Combines teaching qualification with humanities studies. Covers pedagogy and culture. Develops instructional skills. Prepares for education roles.</t>
         </is>
       </c>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Design in Interior Architecture and BA in International Studies</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>DEG-000040</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Design / Architecture</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>Combines interior design with global studies. Covers spatial design and culture. Develops creative and technical skills. Prepares for design careers.</t>
         </is>
       </c>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Design in Product Design and BA in International Studies</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>DEG-000041</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Design / Product</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>Combines product design with global studies. Covers innovation and user-centred design. Develops technical skills. Prepares for design industry roles.</t>
         </is>
       </c>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Medical Science and BA in International Studies</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>DEG-000042</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Medical Science</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Combines medical science with global studies. Covers biology, health systems, and policy. Develops scientific skills. Prepares for health sector roles.</t>
         </is>
       </c>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Design in Animation and BA in International Studies</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>DEG-000043</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>Design / International Studies</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>Combines animation with global cultural studies. Covers storytelling and media production. Develops creative skills. Prepares for animation and media roles.</t>
         </is>
       </c>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Design in Photography and BA in International Studies</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>DEG-000044</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Design / Photography</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>Combines photography with international studies. Covers visual storytelling and culture. Develops artistic skills. Prepares for media and photography roles.</t>
         </is>
       </c>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Commerce and BA in Psychology and Economics</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>DEG-000045</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>Business / Social Science</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>Integrates commerce, psychology, and economics. Covers markets, behaviour, and policy. Develops analytical skills. Prepares for finance and consulting roles.</t>
         </is>
       </c>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="6" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Communication in Creative Writing and BA in International Studies</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>DEG-000046</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Communication / International Studies</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>Combines creative writing with global studies. Covers media, culture, and communication. Develops storytelling skills. Prepares for media and international roles.</t>
         </is>
       </c>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Construction Project Management, BA in International Studies</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>DEG-000047</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>Construction / International Studies</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>Combines construction management with global studies. Covers planning, infrastructure, and policy. Develops leadership skills. Prepares for project management roles.</t>
         </is>
       </c>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Commerce and BA in Psychology</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>DEG-000048</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Business / Psychology</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>Combines business commerce with psychological science. Covers markets, behaviour, and analytics. Develops interdisciplinary skills. Prepares for business and HR roles.</t>
         </is>
       </c>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Bachelor in Transfer Degree</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>DEG-000049</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>General Studies</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>Provides foundational academic coursework for transfer. Develops core academic skills. Focuses on university progression pathways. Prepares students for advanced degrees.</t>
         </is>
       </c>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Bachelor and MBA in Supply Chain Management</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>DEG-000050</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Business / Logistics</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>Integrated program covering supply chain and advanced business management. Covers logistics, operations, and strategy. Develops leadership skills. Prepares for senior management roles.</t>
         </is>
       </c>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Law with English Language Studies</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>DEG-000051</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>English Studies</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>Combines law with advanced study of English linguistics and usage. Builds strong written and verbal reasoning. Prepares for careers in law, media, publishing, or public administration.</t>
         </is>
       </c>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Law with English</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>DEG-000052</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>Combines law with English language and literature studies. Strengthens critical thinking, analysis, and communication. Prepares for careers in law, publishing, education, or media industries.</t>
         </is>
       </c>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Law with Classical Studies</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>DEG-000053</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>Classical Studies</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>Integrates law with ancient Greek and Roman civilizations. Develops analytical and historical interpretation skills. Prepares for careers in law, academia, heritage, or cultural policy sectors.</t>
         </is>
       </c>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Law with Criminology</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>DEG-000054</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Criminology</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>Combines law with the study of crime, justice, and society. Develops understanding of criminal behavior and legal responses. Leads to careers in policing, legal practice, or criminal justice policy.</t>
         </is>
       </c>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Forestry Transfer</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>DEG-000055</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>Forestry (Transfer Program)</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>Provides foundational forestry education for academic transfer pathways. Develops basic ecological and scientific skills. Prepares students for advanced forestry studies. Strengthens academic readiness. Supports progression into specialized forestry degrees.</t>
         </is>
       </c>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="6" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Language and Literature Education</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>DEG-000056</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Education &amp; Language</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>Focuses on teaching languages and literature. Builds pedagogy and communication skills. Graduates work as language teachers.</t>
         </is>
       </c>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Mathematics with Education</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>DEG-000057</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>Mathematics Education</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>Focuses on mathematics teaching and learning methods. Builds pedagogical skills. Graduates work in schools or education roles.</t>
         </is>
       </c>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Italian and Persian</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>DEG-000058</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Language Studies</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>Combines Italian and Persian languages. Builds intercultural communication skills. Graduates work in translation and diplomacy.</t>
         </is>
       </c>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Bachelor of Medical Studies and Doctor of Medicine</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>DEG-000059</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>Medical Pathway</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>Integrated medical training program. Builds clinical and scientific expertise. Graduates become licensed medical practitioners.</t>
         </is>
       </c>
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Bachelor of History Teaching</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>DEG-000060</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>Studies methods of teaching history. Develops pedagogical skills. Focuses on classroom instruction. Graduates work as educators.</t>
         </is>
       </c>
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="6" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>PhD in Fluids Engineering</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>DEG-000061</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>Mechanical Engineering</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>Studies fluid flow and engineering system design. Develops expertise in computational modeling and experimental research. Focuses on industrial and energy applications. Graduates work in research, aerospace, and engineering firms.</t>
         </is>
       </c>
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="6" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>PhD in Food and Biochemical Technology</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>DEG-000062</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Food Science</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>Combines food science with biochemical technologies. Develops expertise in food processing and biochemical research. Focuses on improving food quality and innovation. Graduates work in academia, biotechnology, and food industries.</t>
         </is>
       </c>
+      <c r="G63" s="6" t="n"/>
+      <c r="H63" s="6" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>PhD in Food Systems</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>DEG-000063</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>Food Systems</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <t>Explores food production, distribution, and consumption systems. Develops interdisciplinary research and policy skills. Focuses on sustainability and resilience. Graduates work in academia, government, and nonprofit organizations.</t>
         </is>
       </c>
+      <c r="G64" s="6" t="n"/>
+      <c r="H64" s="6" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>PhD in Gender Studies</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>DEG-000064</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>Gender Studies</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>Explores gender through social, political, and cultural research. Develops critical thinking and interdisciplinary research skills. Focuses on identity and equality. Graduates work in academia, policy, and community organizations.</t>
         </is>
       </c>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="6" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>PhD in Geodesy and Geoinformatics</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>DEG-000065</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>Geospatial Science</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t>Combines geodesy with digital geographic information systems. Develops expertise in spatial analysis and geospatial technologies. Focuses on Earth measurement and mapping. Graduates work in academia, surveying, and GIS industries.</t>
         </is>
       </c>
+      <c r="G66" s="6" t="n"/>
+      <c r="H66" s="6" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>PhD in Geography and Earth Science</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>DEG-000066</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>Earth Science</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>Combines geography with Earth science research. Develops expertise in environmental systems and geospatial analysis. Focuses on understanding Earth's processes. Graduates work in academia, environmental consulting, and government.</t>
         </is>
       </c>
+      <c r="G67" s="6" t="n"/>
+      <c r="H67" s="6" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>PhD in Geometry and Topology</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>DEG-000067</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <t>Studies the properties and structures of geometric spaces. Develops expertise in abstract mathematics and theoretical research. Focuses on advanced mathematical concepts. Graduates work in academia, research, and higher education.</t>
         </is>
       </c>
+      <c r="G68" s="6" t="n"/>
+      <c r="H68" s="6" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>PhD in Geospatial Analytics</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>DEG-000068</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Data Science</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>Studies advanced analysis of geographic and spatial data. Develops expertise in GIS, machine learning, and predictive modeling. Focuses on spatial decision-making. Graduates work in academia, government, and technology industries.</t>
         </is>
       </c>
+      <c r="G69" s="6" t="n"/>
+      <c r="H69" s="6" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>PhD in Grain Science</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>DEG-000069</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>Agricultural Science</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>Studies grain production, processing, and quality. Develops expertise in cereal chemistry and agricultural research. Focuses on food quality and sustainable production. Graduates work in academia, agriculture, and food industries.</t>
         </is>
       </c>
+      <c r="G70" s="6" t="n"/>
+      <c r="H70" s="6" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>PhD in Health Economics and Policy</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>DEG-000070</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>Health Economics</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>Integrates economic analysis with healthcare policy research. Develops expertise in health financing and policy evaluation. Focuses on improving health systems. Graduates work in academia, government, and healthcare organizations.</t>
         </is>
       </c>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="6" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>PhD in Hispanic Studies and Comparative Literature</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>DEG-000071</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>Combines Hispanic studies with comparative literary research. Develops expertise in literary analysis and cross-cultural interpretation. Focuses on global literary traditions. Graduates work in academia, publishing, and education.</t>
         </is>
       </c>
+      <c r="G72" s="6" t="n"/>
+      <c r="H72" s="6" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>PhD in History of Art and Archaeology</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>DEG-000072</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Art History</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>Combines art history with archaeological research. Develops expertise in material culture and historical interpretation. Focuses on ancient and historical artifacts. Graduates work in academia, museums, and heritage organizations.</t>
         </is>
       </c>
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="6" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>PhD in Laser, Photonics and Vision</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>DEG-000073</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>Physics</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>Studies laser systems, photonics, and optical vision technologies. Develops expertise in optics, imaging, and applied physics. Focuses on light-based technologies. Graduates work in academia, research labs, and optical industries.</t>
         </is>
       </c>
+      <c r="G74" s="6" t="n"/>
+      <c r="H74" s="6" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>PhD in Latin American Cultural Studies</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>DEG-000074</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>Cultural Studies</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>Explores cultural production, identity, and history in Latin America. Develops expertise in literary and cultural theory. Focuses on regional cultural expression. Graduates work in academia, publishing, and cultural organizations.</t>
         </is>
       </c>
+      <c r="G75" s="6" t="n"/>
+      <c r="H75" s="6" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>PhD in Leadership and Policy Studies in Education</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>DEG-000075</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>Examines leadership and policy in educational systems. Develops expertise in administration, policy analysis, and school leadership. Focuses on educational improvement. Graduates work in academia, schools, and government agencies.</t>
         </is>
       </c>
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="6" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>PhD in Management Finance</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>DEG-000076</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <t>Integrates financial management with organizational strategy. Develops expertise in corporate finance, investment, and risk management. Focuses on financial decision-making. Graduates work in finance, corporations, and consulting.</t>
         </is>
       </c>
+      <c r="G77" s="6" t="n"/>
+      <c r="H77" s="6" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>PhD in Marine Engine Engineering</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>DEG-000077</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>Marine Engineering</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>Focuses on design and maintenance of marine propulsion systems. Develops expertise in mechanical and marine systems engineering. Focuses on ship engine performance. Graduates work in shipping, engineering, and maritime industries.</t>
         </is>
       </c>
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="6" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>PhD in Marketing and Entrepreneurship</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>DEG-000078</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>Entrepreneurship</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>Studies marketing strategies for new ventures and startups. Develops expertise in innovation, branding, and business development. Focuses on entrepreneurial growth. Graduates work in startups, consulting, and business development.</t>
         </is>
       </c>
+      <c r="G79" s="6" t="n"/>
+      <c r="H79" s="6" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>PhD in Phonetics and Phonology</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>DEG-000079</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>PhD</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>Linguistics</t>
         </is>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>Combines speech sound analysis with language sound systems. Develops expertise in linguistic theory and speech research. Focuses on sound structure and communication. Graduates work in academia, linguistics, and speech technology.</t>
         </is>
       </c>
+      <c r="G80" s="6" t="n"/>
+      <c r="H80" s="6" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Nursing and Allied Health</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>DEG-000080</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>Nursing and Allied Health</t>
         </is>
       </c>
-      <c r="E81" t="n">
-        <v>2</v>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="E81" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>Studies basic nursing and healthcare support. Develops clinical and patient care skills. Focuses on healthcare services. Prepares graduates for healthcare support roles.</t>
         </is>
       </c>
+      <c r="G81" s="6" t="n"/>
+      <c r="H81" s="6" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Medical Assistant</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>DEG-000081</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>Medical Assistance</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v>2</v>
-      </c>
-      <c r="F82" t="inlineStr">
+      <c r="E82" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <t>Studies clinical and administrative healthcare support. Develops patient care skills. Focuses on medical office practice. Prepares graduates for healthcare support roles.</t>
         </is>
       </c>
+      <c r="G82" s="6" t="n"/>
+      <c r="H82" s="6" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>Associate of Science in Radiography</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>DEG-000082</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Radiography</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v>2</v>
-      </c>
-      <c r="F83" t="inlineStr">
+      <c r="E83" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>Studies medical imaging and radiographic techniques. Develops imaging, patient care, and technical skills. Focuses on diagnostic imaging procedures. Graduates work in hospitals and medical imaging departments.</t>
         </is>
       </c>
+      <c r="G83" s="6" t="n"/>
+      <c r="H83" s="6" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Associate of Arts in Marketing</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>DEG-000083</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="E84" t="n">
-        <v>2</v>
-      </c>
-      <c r="F84" t="inlineStr">
+      <c r="E84" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>Studies marketing strategies and consumer behavior. Develops communication, analytical, and promotional skills. Focuses on branding, advertising, and market research. Graduates work in marketing, sales, and retail.</t>
         </is>
       </c>
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="6" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Dental Hygiene</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>DEG-000084</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>Dental Hygiene</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v>2</v>
-      </c>
-      <c r="F85" t="inlineStr">
+      <c r="E85" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>Studies preventive dental care and oral health. Develops clinical, patient care, and communication skills. Focuses on dental hygiene procedures and education. Graduates work in dental clinics and healthcare facilities.</t>
         </is>
       </c>
+      <c r="G85" s="6" t="n"/>
+      <c r="H85" s="6" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Radiography</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>DEG-000085</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="6" t="inlineStr">
         <is>
           <t>Radiography</t>
         </is>
       </c>
-      <c r="E86" t="n">
-        <v>2</v>
-      </c>
-      <c r="F86" t="inlineStr">
+      <c r="E86" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>Studies diagnostic imaging and radiographic procedures. Develops imaging, patient care, and technical skills. Focuses on producing medical images for diagnosis. Graduates work in hospitals and diagnostic imaging centers.</t>
         </is>
       </c>
+      <c r="G86" s="6" t="n"/>
+      <c r="H86" s="6" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Diagnostic Medical Sonography</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>DEG-000086</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>Diagnostic Medical Sonography</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>2</v>
-      </c>
-      <c r="F87" t="inlineStr">
+      <c r="E87" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>Studies ultrasound imaging and patient care. Develops diagnostic imaging, technical, and clinical skills. Focuses on safe and accurate medical sonography. Prepares graduates for careers as diagnostic medical sonographers.</t>
         </is>
       </c>
+      <c r="G87" s="6" t="n"/>
+      <c r="H87" s="6" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Associate of Science in Music Production</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>DEG-000087</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>Music Production</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>2</v>
-      </c>
-      <c r="F88" t="inlineStr">
+      <c r="E88" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>Studies audio recording, music technology, and production. Develops recording, editing, and sound design skills. Focuses on creating professional music productions. Graduates work in recording studios and media production.</t>
         </is>
       </c>
+      <c r="G88" s="6" t="n"/>
+      <c r="H88" s="6" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>Associate of Applied Science</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>DEG-000088</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>Applied Science</t>
         </is>
       </c>
-      <c r="E89" t="n">
-        <v>2</v>
-      </c>
-      <c r="F89" t="inlineStr">
+      <c r="E89" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>Studies practical scientific and technical applications. Develops laboratory, technical, and problem-solving skills. Focuses on career-ready scientific knowledge. Graduates work in technical, healthcare, and industrial roles.</t>
         </is>
       </c>
+      <c r="G89" s="6" t="n"/>
+      <c r="H89" s="6" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>Associate of Science in Nursing</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>DEG-000089</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>Nursing</t>
         </is>
       </c>
-      <c r="E90" t="n">
-        <v>2</v>
-      </c>
-      <c r="F90" t="inlineStr">
+      <c r="E90" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>Studies nursing science and patient-centered care. Develops clinical, communication, and healthcare skills. Focuses on safe nursing practice and health promotion. Graduates work in hospitals, clinics, and healthcare facilities.</t>
         </is>
       </c>
+      <c r="G90" s="6" t="n"/>
+      <c r="H90" s="6" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>Associate of Arts</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>DEG-000090</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v>2</v>
-      </c>
-      <c r="F91" t="inlineStr">
+      <c r="E91" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>Studies humanities, social sciences, and communication. Develops critical thinking, writing, and analytical skills. Focuses on broad academic preparation. Graduates continue higher education or enter diverse professional fields.</t>
         </is>
       </c>
+      <c r="G91" s="6" t="n"/>
+      <c r="H91" s="6" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>Associate of Arts Degree</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>DEG-000091</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="6" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="E92" t="n">
-        <v>2</v>
-      </c>
-      <c r="F92" t="inlineStr">
+      <c r="E92" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <t>Studies a broad range of humanities and social sciences. Develops communication, research, and critical thinking skills. Focuses on transferable academic knowledge. Graduates continue higher education or pursue entry-level careers.</t>
         </is>
       </c>
+      <c r="G92" s="6" t="n"/>
+      <c r="H92" s="6" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>Associate of Nursing</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>DEG-000092</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Nursing</t>
         </is>
       </c>
-      <c r="E93" t="n">
-        <v>2</v>
-      </c>
-      <c r="F93" t="inlineStr">
+      <c r="E93" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>Studies patient care and foundational nursing practice. Develops clinical, communication, and healthcare skills. Focuses on evidence-based nursing and patient safety. Graduates work in hospitals, clinics, and healthcare facilities.</t>
         </is>
       </c>
+      <c r="G93" s="6" t="n"/>
+      <c r="H93" s="6" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>Associate of Science in Business</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>DEG-000093</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="E94" t="n">
-        <v>2</v>
-      </c>
-      <c r="F94" t="inlineStr">
+      <c r="E94" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <t>Studies core business principles and organizational practices. Develops communication, management, and analytical skills. Focuses on finance, marketing, and operations. Graduates work in business support, retail, and administration.</t>
         </is>
       </c>
+      <c r="G94" s="6" t="n"/>
+      <c r="H94" s="6" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>Associate of Science</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>DEG-000094</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="E95" t="n">
-        <v>2</v>
-      </c>
-      <c r="F95" t="inlineStr">
+      <c r="E95" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>Studies foundational scientific concepts and methods. Develops laboratory, analytical, and problem-solving skills. Focuses on biology, chemistry, and scientific inquiry. Graduates continue science studies or work in technical fields.</t>
         </is>
       </c>
+      <c r="G95" s="6" t="n"/>
+      <c r="H95" s="6" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>Associate of Science in Business Administration</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>DEG-000095</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="6" t="inlineStr">
         <is>
           <t>Business Administration</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>2</v>
-      </c>
-      <c r="F96" t="inlineStr">
+      <c r="E96" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <t>Studies business operations and management fundamentals. Develops organizational, communication, and leadership skills. Focuses on business strategy and workplace effectiveness. Graduates work in administration, sales, and operations.</t>
         </is>
       </c>
+      <c r="G96" s="6" t="n"/>
+      <c r="H96" s="6" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>Associate of Science in Biology and Ecology</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>DEG-000096</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>Biology and Ecology</t>
         </is>
       </c>
-      <c r="E97" t="n">
-        <v>2</v>
-      </c>
-      <c r="F97" t="inlineStr">
+      <c r="E97" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>Studies biological systems and ecological processes. Develops laboratory, fieldwork, and analytical skills. Focuses on ecosystems, biodiversity, and environmental science. Graduates work in environmental organizations and laboratories.</t>
         </is>
       </c>
+      <c r="G97" s="6" t="n"/>
+      <c r="H97" s="6" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Accounting</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>DEG-000097</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="6" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="E98" t="n">
-        <v>2</v>
-      </c>
-      <c r="F98" t="inlineStr">
+      <c r="E98" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <t>Studies accounting principles and financial reporting. Develops bookkeeping, financial analysis, and accounting software skills. Focuses on business finance and compliance. Graduates work in accounting, bookkeeping, and finance support.</t>
         </is>
       </c>
+      <c r="G98" s="6" t="n"/>
+      <c r="H98" s="6" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>Associate of Applied Science in Hospitality Management</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>DEG-000098</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>Hospitality Management</t>
         </is>
       </c>
-      <c r="E99" t="n">
-        <v>2</v>
-      </c>
-      <c r="F99" t="inlineStr">
+      <c r="E99" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>Studies hospitality operations and customer service management. Develops leadership, communication, and operational skills. Focuses on hotels, tourism, and guest satisfaction. Graduates work in hospitality, tourism, and hotel management.</t>
         </is>
       </c>
+      <c r="G99" s="6" t="n"/>
+      <c r="H99" s="6" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>Associate of Science in Computer Science</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>DEG-000099</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>Computer Science</t>
         </is>
       </c>
-      <c r="E100" t="n">
-        <v>2</v>
-      </c>
-      <c r="F100" t="inlineStr">
+      <c r="E100" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <t>Studies computing principles and software development. Develops programming, analytical, and technical problem-solving skills. Focuses on algorithms, databases, and computer systems. Graduates work in IT support and software development.</t>
         </is>
       </c>
+      <c r="G100" s="6" t="n"/>
+      <c r="H100" s="6" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>Associate of Arts in Business Administration</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>DEG-000100</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>Associate</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>Business Administration</t>
         </is>
       </c>
-      <c r="E101" t="n">
-        <v>2</v>
-      </c>
-      <c r="F101" t="inlineStr">
+      <c r="E101" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <t>Studies business operations and organizational management. Develops leadership, communication, and administrative skills. Focuses on finance, marketing, and business practices. Graduates work in administration, retail, and business support.</t>
         </is>
       </c>
+      <c r="G101" s="6" t="n"/>
+      <c r="H101" s="6" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>

--- a/apps/api/data/excel_templates/degrees.xlsx
+++ b/apps/api/data/excel_templates/degrees.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>BACHELOR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>PHD</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>ASSOCIATE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
